--- a/WEB-ScSc/ExcelExamples/Russian-Русский.xlsx
+++ b/WEB-ScSc/ExcelExamples/Russian-Русский.xlsx
@@ -8094,12 +8094,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8107,12 +8101,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8120,12 +8108,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8133,12 +8115,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8146,12 +8122,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8159,12 +8129,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,12 +8136,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8185,12 +8143,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8198,12 +8150,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8211,12 +8157,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8275,12 +8215,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8288,12 +8222,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8301,12 +8229,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8314,12 +8236,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8327,12 +8243,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8340,12 +8250,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8353,12 +8257,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8366,12 +8264,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8379,12 +8271,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8392,12 +8278,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8456,12 +8336,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8469,12 +8343,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8482,12 +8350,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8495,12 +8357,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8508,12 +8364,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8521,12 +8371,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8534,12 +8378,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8547,12 +8385,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8560,12 +8392,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8573,12 +8399,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8637,12 +8457,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8650,12 +8464,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8663,12 +8471,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8676,12 +8478,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8689,12 +8485,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8702,12 +8492,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8715,12 +8499,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8728,12 +8506,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8741,12 +8513,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8754,12 +8520,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8818,12 +8578,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8831,12 +8585,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8844,12 +8592,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8857,12 +8599,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8870,12 +8606,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8883,12 +8613,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8896,12 +8620,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8909,12 +8627,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8922,12 +8634,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8935,12 +8641,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8999,12 +8699,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9012,12 +8706,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9025,12 +8713,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9038,12 +8720,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9051,12 +8727,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9064,12 +8734,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9077,12 +8741,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9090,12 +8748,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9103,12 +8755,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9116,12 +8762,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9180,12 +8820,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9193,12 +8827,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9206,12 +8834,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9219,12 +8841,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9232,12 +8848,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9245,12 +8855,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9258,12 +8862,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9271,12 +8869,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9284,12 +8876,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9297,12 +8883,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9361,12 +8941,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9374,12 +8948,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9387,12 +8955,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9400,12 +8962,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9413,12 +8969,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9426,12 +8976,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9439,12 +8983,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9452,12 +8990,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9465,12 +8997,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9478,12 +9004,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9542,12 +9062,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9555,12 +9069,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9568,12 +9076,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9581,12 +9083,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9594,16 +9090,11 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9616,15 +9107,11 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9632,12 +9119,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9645,12 +9126,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9658,12 +9133,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9671,12 +9140,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9837,12 +9300,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9850,12 +9307,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9863,12 +9314,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9876,12 +9321,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9889,12 +9328,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9902,12 +9335,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9915,12 +9342,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9928,12 +9349,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9941,16 +9356,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9958,12 +9368,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10022,12 +9426,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10035,12 +9433,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10048,12 +9440,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10061,12 +9447,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10074,12 +9454,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10087,12 +9461,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10100,12 +9468,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10113,12 +9475,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10126,12 +9482,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10139,12 +9489,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10203,12 +9547,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10216,12 +9554,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10229,12 +9561,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10242,12 +9568,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10255,12 +9575,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10268,12 +9582,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10281,12 +9589,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10294,12 +9596,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10307,12 +9603,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10320,12 +9610,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10399,13 +9683,11 @@
           <t>Талмуд 12 класс</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10428,13 +9710,11 @@
           <t>Талмуд 12 класс</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10457,13 +9737,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Традиция 10 класс</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10486,13 +9764,11 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10515,9 +9791,6 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10530,15 +9803,11 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10551,11 +9820,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10563,12 +9827,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10576,12 +9834,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10589,12 +9841,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10653,12 +9899,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10666,12 +9906,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10679,16 +9913,11 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10711,9 +9940,6 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10736,9 +9962,6 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10751,15 +9974,11 @@
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="1" t="inlineStr">
         <is>
           <t>Языковая лаборатория 8-10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10767,12 +9986,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10780,12 +9993,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10793,12 +10000,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10806,12 +10007,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10870,12 +10065,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10883,12 +10072,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10896,12 +10079,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10909,12 +10086,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10922,12 +10093,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10935,12 +10100,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10948,16 +10107,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10965,16 +10119,11 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10982,16 +10131,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10999,12 +10143,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11063,12 +10201,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11076,12 +10208,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11089,12 +10215,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11102,12 +10222,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11115,12 +10229,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11128,12 +10236,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11141,16 +10243,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11158,16 +10255,11 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11175,16 +10267,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Курс безопасности 8-10</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11192,12 +10279,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11256,12 +10337,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11269,12 +10344,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11307,7 +10376,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11315,7 +10383,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -11336,7 +10403,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11344,7 +10410,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -11365,7 +10430,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11383,10 +10447,6 @@
           <t>Информатика 10 класс</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11409,9 +10469,6 @@
           <t>Информатика 11 класс</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11434,9 +10491,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11459,9 +10513,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11484,9 +10535,6 @@
           <t>Информатика 10 класс</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11545,7 +10593,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -11556,9 +10603,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11566,7 +10610,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -11577,9 +10620,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11602,9 +10642,6 @@
           <t>Информатика-Электроника 12 класс</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11627,9 +10664,6 @@
           <t>Информатика-Электроника 11 класс</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11652,9 +10686,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11677,9 +10708,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11702,9 +10730,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11727,9 +10752,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11747,10 +10769,6 @@
           <t>Информатика-Электроника 11 класс</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11758,16 +10776,11 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Информатика-Электроника 12 класс</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11846,8 +10859,6 @@
           <t>Талмуд 11 класс</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11875,8 +10886,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11904,8 +10913,6 @@
           <t>Философия 12 класс</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11933,8 +10940,6 @@
           <t>Философия 12 класс</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11952,14 +10957,11 @@
           <t>Иврит 12 класс</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11967,12 +10969,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11980,12 +10976,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11993,12 +10983,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12006,12 +10990,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12019,12 +10997,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12204,12 +11176,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12227,10 +11193,6 @@
           <t>Иврит 12 класс</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12248,10 +11210,6 @@
           <t>Иврит 11 класс</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12269,10 +11227,6 @@
           <t>Иврит 11 класс</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12280,16 +11234,11 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Иврит 12 класс</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12297,16 +11246,11 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12314,16 +11258,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Иврит-Физика 12 класс</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12331,12 +11270,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12344,12 +11277,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12357,12 +11284,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12421,12 +11342,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12434,12 +11349,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12447,12 +11356,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12465,11 +11368,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12482,11 +11380,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12499,15 +11392,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="18" t="inlineStr">
         <is>
           <t>Математика 12 класс лаборатория</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12520,15 +11409,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Математика 12 класс лаборатория</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12541,15 +11426,11 @@
           <t>Математика 10 класс группы</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" s="20" t="inlineStr">
         <is>
           <t>Математика 12 класс группы</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12562,15 +11443,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Математика 12 класс группы</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12583,15 +11460,11 @@
           <t>Математика 12 класс группы</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12650,12 +11523,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12663,12 +11530,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12681,11 +11542,6 @@
           <t>Английский язык 11 класс группы</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12698,11 +11554,6 @@
           <t>Английский язык 11 класс группы</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12715,11 +11566,6 @@
           <t>Английский язык 12 класс группы</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12737,10 +11583,6 @@
           <t>Английский язык 11 класс группы</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12758,10 +11600,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12779,10 +11617,6 @@
           <t>Английский язык 12 класс группы</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12790,16 +11624,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Английский язык 12 класс группы</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12807,16 +11636,11 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Английский язык 10 класс</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12875,12 +11699,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12898,10 +11716,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12919,10 +11733,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12940,10 +11750,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12961,10 +11767,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12982,10 +11784,6 @@
           <t>Английский язык 11 класс группы</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13003,10 +11801,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13024,10 +11818,6 @@
           <t>Английский язык 12 класс группы</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13035,16 +11825,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Английский язык 12 класс группы</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13052,12 +11837,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13116,12 +11895,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13129,12 +11902,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13142,12 +11909,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13155,16 +11916,11 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Литература 12 класс</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13172,16 +11928,11 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" s="26" t="inlineStr">
         <is>
           <t>Литература 11 класс</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13189,16 +11940,11 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Литература 12 класс</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13206,16 +11952,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" s="26" t="inlineStr">
         <is>
           <t>Литература 11 класс</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13223,12 +11964,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13236,12 +11971,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13249,12 +11978,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13313,7 +12036,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13324,9 +12046,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13349,9 +12068,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13374,9 +12090,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13399,9 +12112,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13424,9 +12134,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13449,9 +12156,6 @@
           <t>Математика 12 класс лаборатория</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13474,9 +12178,6 @@
           <t>Математика 12 класс лаборатория</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13499,9 +12200,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13509,7 +12207,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13520,9 +12217,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13530,12 +12224,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13609,13 +12297,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13638,13 +12324,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13667,13 +12351,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13681,7 +12363,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13692,13 +12373,11 @@
           <t>Граждановедение 12 класс</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13706,7 +12385,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13717,9 +12395,6 @@
           <t>Граждановедение 12 класс</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13727,7 +12402,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13738,9 +12412,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13748,12 +12419,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13761,12 +12426,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13774,12 +12433,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13787,12 +12440,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13851,8 +12498,6 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13868,7 +12513,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13876,8 +12520,6 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13893,7 +12535,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13901,8 +12542,6 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13918,7 +12557,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13926,8 +12564,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13943,7 +12579,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13951,8 +12586,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -13968,7 +12601,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13976,8 +12608,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" s="28" t="inlineStr">
         <is>
           <t>Недельная Тора 11 класс</t>
@@ -13993,7 +12623,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14001,8 +12630,6 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -14018,7 +12645,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14026,8 +12652,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -14043,7 +12667,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14051,8 +12674,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -14068,7 +12689,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14076,8 +12696,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" s="33" t="inlineStr">
         <is>
           <t>Недельная Тора 12 класс</t>
@@ -14093,7 +12711,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14162,7 +12779,6 @@
           <t>Традиция 8 класс</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="35" t="inlineStr">
         <is>
           <t>Искусство 12 класс</t>
@@ -14173,7 +12789,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14206,7 +12821,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14219,7 +12833,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" s="36" t="inlineStr">
         <is>
           <t>Искусство 9 класс</t>
@@ -14230,8 +12843,6 @@
           <t>Искусство 8 класс</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14239,16 +12850,11 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14256,12 +12862,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14269,12 +12869,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14287,11 +12881,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14299,12 +12888,6 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14312,12 +12895,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14325,12 +12902,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14409,8 +12980,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14438,8 +13007,6 @@
           <t>История Израиля 9 класс</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14467,8 +13034,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14476,8 +13041,6 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -14488,8 +13051,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14497,8 +13058,6 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Empty</t>
@@ -14514,7 +13073,6 @@
           <t>Талмуд 10 класс</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14522,16 +13080,11 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="41" t="inlineStr">
         <is>
           <t>Практика иврита</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14539,16 +13092,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14556,16 +13104,11 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14573,16 +13116,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14590,16 +13128,11 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14789,11 +13322,6 @@
           <t>Русский язык 11 класс</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14806,11 +13334,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14823,11 +13346,6 @@
           <t>Русский язык 10 класс</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14840,11 +13358,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14857,11 +13370,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14874,11 +13382,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14891,15 +13394,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="44" t="inlineStr">
         <is>
           <t>Русский язык 12 класс</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14912,15 +13411,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="44" t="inlineStr">
         <is>
           <t>Русский язык 12 класс</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14928,16 +13423,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="42" t="inlineStr">
         <is>
           <t>Русский язык 11 класс</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14945,12 +13435,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15009,16 +13493,11 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="45" t="inlineStr">
         <is>
           <t>Физическая культура 12 класс</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15026,16 +13505,11 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="45" t="inlineStr">
         <is>
           <t>Физическая культура 12 класс</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15048,15 +13522,11 @@
           <t>Физическая культура 9 класс</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="47" t="inlineStr">
         <is>
           <t>Физическая культура 11 класс</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15069,15 +13539,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="48" t="inlineStr">
         <is>
           <t>Физическая культура 10 класс</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15090,11 +13556,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15107,11 +13568,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15124,11 +13580,6 @@
           <t>Физическая культура 9 класс</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15141,11 +13592,6 @@
           <t>Физическая культура 8 класс</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15158,11 +13604,6 @@
           <t>Физическая культура 8 класс</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15175,11 +13616,6 @@
           <t>Физическая культура 11 класс</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15243,11 +13679,6 @@
           <t>Английский язык 10 класс лаборатория</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15265,10 +13696,6 @@
           <t>Английский язык 10 класс лаборатория</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15286,10 +13713,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15307,10 +13730,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15328,10 +13747,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15349,10 +13764,6 @@
           <t>Английский язык 11 класс группы</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15370,10 +13781,6 @@
           <t>Английский язык 10 класс лаборатория</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15391,10 +13798,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15402,16 +13805,11 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15419,12 +13817,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15488,19 +13880,16 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" s="51" t="inlineStr">
         <is>
           <t>Математика 9 класс</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="52" t="inlineStr">
         <is>
           <t>Математика 10 класс</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15513,19 +13902,16 @@
           <t>Математика 11 класс группы</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" s="51" t="inlineStr">
         <is>
           <t>Математика 9 класс</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="52" t="inlineStr">
         <is>
           <t>Математика 10 класс</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15538,19 +13924,16 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" s="54" t="inlineStr">
         <is>
           <t>Математика 11 класс</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Математика 9 класс</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15563,19 +13946,16 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15588,15 +13968,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15609,11 +13985,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15626,11 +13997,6 @@
           <t>Математика 11 класс группы</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15643,11 +14009,6 @@
           <t>Математика 10 класс группы</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15660,11 +14021,6 @@
           <t>Математика 11 класс группы</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15677,11 +14033,6 @@
           <t>Математика 10 класс</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15765,7 +14116,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15798,7 +14148,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15831,7 +14180,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15864,7 +14212,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15897,7 +14244,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15930,7 +14276,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15963,7 +14308,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15996,7 +14340,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16029,7 +14372,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16062,7 +14404,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16121,16 +14462,11 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="62" t="inlineStr">
         <is>
           <t>Электроника 10 класс</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16138,16 +14474,11 @@
           <t>10:00-10:40</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="62" t="inlineStr">
         <is>
           <t>Электроника 10 класс</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16155,20 +14486,16 @@
           <t>10:45-11:30</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16176,20 +14503,16 @@
           <t>11:30-12:15</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" s="63" t="inlineStr">
         <is>
           <t>Физика 9 класс</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16197,20 +14520,16 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" s="63" t="inlineStr">
         <is>
           <t>Физика 9 класс</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16218,12 +14537,6 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16236,11 +14549,6 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16253,11 +14561,6 @@
           <t>Электроника 9 класс</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16270,11 +14573,6 @@
           <t>Электроника 9 класс</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16282,12 +14580,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16346,16 +14638,11 @@
           <t>9:15-10:00</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="65" t="inlineStr">
         <is>
           <t>История 9 класс</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16373,14 +14660,11 @@
           <t>Граждановедение</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="66" t="inlineStr">
         <is>
           <t>Граждановедение</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16398,14 +14682,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16423,14 +14704,11 @@
           <t>Empty</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" s="67" t="inlineStr">
         <is>
           <t>История 8 класс</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16438,20 +14716,16 @@
           <t>12:20-13:00</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" s="68" t="inlineStr">
         <is>
           <t>Граждановедение 10 класс</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16459,16 +14733,11 @@
           <t>14:00-14:45</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" s="69" t="inlineStr">
         <is>
           <t>Граждановедение 9 класс</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16476,16 +14745,11 @@
           <t>14:55-15:40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Empty</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16493,16 +14757,11 @@
           <t>15:50-16:35</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" s="69" t="inlineStr">
         <is>
           <t>Граждановедение 9 класс</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16510,12 +14769,6 @@
           <t>16:40-17:25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16523,12 +14776,6 @@
           <t>17:30-18:15</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17213,14 +15460,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Кабинет 12</t>
@@ -17228,14 +15475,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Кабинет 11</t>
@@ -17243,14 +15490,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Кабинет 10</t>
@@ -17258,14 +15505,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Кабинет 9</t>
@@ -17273,14 +15520,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Кабинет 8</t>
@@ -17293,7 +15540,6 @@
           <t>9 Английский 3/4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>1</v>
       </c>
@@ -17302,7 +15548,6 @@
           <t>9; 10</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17310,7 +15555,6 @@
           <t>9 Английский 3/4/5</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>1</v>
       </c>
@@ -17319,7 +15563,6 @@
           <t>9; 10</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17327,7 +15570,6 @@
           <t>9 Английский 5</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>1</v>
       </c>
@@ -17336,7 +15578,6 @@
           <t>9; 10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17344,7 +15585,6 @@
           <t>8-10 Лаборатория</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>1</v>
       </c>
@@ -17353,7 +15593,6 @@
           <t>10; 9; 8</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17361,7 +15600,6 @@
           <t>8-10 Безопасность</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>1</v>
       </c>
@@ -17370,7 +15608,6 @@
           <t>8; 9; 10</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17378,7 +15615,6 @@
           <t>9-10 Программирование</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>1</v>
       </c>
@@ -17387,7 +15623,6 @@
           <t>9; 10</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17395,7 +15630,6 @@
           <t>11 Информатика/Электроника лаб</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>1</v>
       </c>
@@ -17404,7 +15638,6 @@
           <t>11; 8</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17438,7 +15671,6 @@
           <t>Кабинет 12</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17446,7 +15678,6 @@
           <t>Кабинет 11</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17454,7 +15685,6 @@
           <t>Кабинет 10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17462,7 +15692,6 @@
           <t>Кабинет 9</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17470,7 +15699,6 @@
           <t>Кабинет 8</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17478,7 +15706,6 @@
           <t>Учительская</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17486,7 +15713,6 @@
           <t>Молитвенный зал</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17494,7 +15720,6 @@
           <t>Компьютерный класс</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17502,7 +15727,6 @@
           <t>Кабинет консультанта</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17510,7 +15734,6 @@
           <t>Практический кабинет</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18887,7 +17110,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18923,7 +17145,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18959,7 +17180,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18995,7 +17215,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19031,7 +17250,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19067,7 +17285,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19103,7 +17320,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19139,7 +17355,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19175,7 +17390,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19211,7 +17425,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19247,7 +17460,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19283,7 +17495,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19319,7 +17530,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19355,7 +17565,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19391,7 +17600,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19427,7 +17635,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19463,7 +17670,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19499,7 +17705,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19535,7 +17740,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19571,7 +17775,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19607,7 +17810,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19643,7 +17845,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19679,7 +17880,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19715,7 +17915,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19751,7 +17950,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19787,7 +17985,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19823,7 +18020,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19859,7 +18055,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19895,7 +18090,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19931,7 +18125,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19967,7 +18160,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -20003,7 +18195,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -20039,7 +18230,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20075,7 +18265,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20111,7 +18300,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20147,7 +18335,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20183,7 +18370,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20219,7 +18405,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20255,7 +18440,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20291,7 +18475,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -20327,7 +18510,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20363,7 +18545,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20399,7 +18580,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20435,7 +18615,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20471,7 +18650,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20507,7 +18685,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20543,7 +18720,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20579,7 +18755,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20615,7 +18790,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20651,7 +18825,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20687,7 +18860,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20723,7 +18895,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20759,7 +18930,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20795,7 +18965,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20831,7 +19000,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20867,7 +19035,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20903,7 +19070,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20939,7 +19105,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20975,7 +19140,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21011,7 +19175,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21047,7 +19210,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21083,7 +19245,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21119,7 +19280,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21155,7 +19315,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21191,7 +19350,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21227,7 +19385,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21263,7 +19420,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21299,7 +19455,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21335,7 +19490,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -21371,7 +19525,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -21407,7 +19560,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -21443,7 +19595,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21479,7 +19630,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21515,7 +19665,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21551,7 +19700,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21587,7 +19735,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21623,7 +19770,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21659,7 +19805,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21695,7 +19840,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -21731,7 +19875,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21767,7 +19910,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21803,7 +19945,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21839,7 +19980,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21875,7 +20015,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21911,7 +20050,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21947,7 +20085,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -21983,7 +20120,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22019,7 +20155,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22055,7 +20190,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22091,7 +20225,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22127,7 +20260,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22163,7 +20295,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22199,7 +20330,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22235,7 +20365,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -22271,7 +20400,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -22307,7 +20435,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -22343,7 +20470,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -22379,7 +20505,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -22415,7 +20540,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -22451,7 +20575,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22487,7 +20610,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22523,7 +20645,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -22559,7 +20680,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -22595,7 +20715,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -22631,7 +20750,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -22667,7 +20785,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -22703,7 +20820,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22739,7 +20855,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -22775,7 +20890,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -22811,7 +20925,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -22847,7 +20960,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -22883,7 +20995,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -22919,7 +21030,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -22955,7 +21065,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -22991,7 +21100,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23027,7 +21135,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -23063,7 +21170,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -23099,7 +21205,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -23135,7 +21240,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23171,7 +21275,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23207,7 +21310,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -23243,7 +21345,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -23279,7 +21380,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23315,7 +21415,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23351,7 +21450,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -23387,7 +21485,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -23423,7 +21520,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -23459,7 +21555,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -23495,7 +21590,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -23531,7 +21625,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -23567,7 +21660,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -23603,7 +21695,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -23639,7 +21730,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -23675,7 +21765,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -23711,7 +21800,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -23747,7 +21835,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -23783,7 +21870,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -23819,7 +21905,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -23855,7 +21940,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -23891,7 +21975,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -23927,7 +22010,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -23963,7 +22045,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -23999,7 +22080,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -24035,7 +22115,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -24071,7 +22150,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -24107,7 +22185,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -24143,7 +22220,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -24179,7 +22255,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -24215,7 +22290,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -24251,7 +22325,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -24287,7 +22360,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -24323,7 +22395,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -24359,7 +22430,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -24395,7 +22465,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -24431,7 +22500,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -24467,7 +22535,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -24503,7 +22570,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -24539,7 +22605,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -24575,7 +22640,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -24611,7 +22675,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -24647,7 +22710,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -24683,7 +22745,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -24719,7 +22780,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -24755,7 +22815,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -24791,7 +22850,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -24827,7 +22885,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -24863,7 +22920,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -24899,7 +22955,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -24935,7 +22990,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -24971,7 +23025,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -25007,7 +23060,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -25043,7 +23095,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -25079,7 +23130,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -25115,7 +23165,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -25151,7 +23200,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -25187,7 +23235,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -25223,7 +23270,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -25259,7 +23305,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -25295,7 +23340,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -25331,7 +23375,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -25367,7 +23410,6 @@
           <t>#000000</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
